--- a/sources/metaPee/combined/subexposure_views/yes/Plot/exposures_meta_analysis_bladder_cancer_combined.xlsx
+++ b/sources/metaPee/combined/subexposure_views/yes/Plot/exposures_meta_analysis_bladder_cancer_combined.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -883,20 +883,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>oleic_acid</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr"/>
@@ -905,16 +905,16 @@
       </c>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>1969</v>
+        <v>500</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>940</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oleic_acid</t>
+          <t>omega_9_fatty_acids</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -945,20 +945,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>omega_9_fatty_acids</t>
+          <t>vitamin_b3</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr"/>
@@ -967,604 +967,628 @@
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>500</v>
+        <v>561</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>250</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vitamin_b3</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="4" t="n">
-        <v>0</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>561</v>
+        <v>2541</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>322</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>4914</v>
+        <v>101981</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>351</v>
+        <v>906</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+        <v>1.27</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>642.3</v>
+      </c>
       <c r="H19" s="4" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr"/>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.191210142468675</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>2541</v>
+        <v>122821</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1268</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+        <v>0.98</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2.28</v>
+      </c>
       <c r="H20" s="4" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr"/>
+        <v>45.8</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0.1427001294834398</v>
+      </c>
       <c r="J20" s="2" t="n">
-        <v>101981</v>
+        <v>126541</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>906</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0.55</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.5</v>
+        <v>71.5</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.1781451106552655</v>
+        <v>0.13348290126051</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>203114</v>
+        <v>161440</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2164</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>whole_grain_intake</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>29.67</v>
+      </c>
       <c r="H22" s="4" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr"/>
+        <v>75.2</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0.2815357195367387</v>
+      </c>
       <c r="J22" s="2" t="n">
-        <v>4359</v>
+        <v>219042</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>831</v>
+        <v>5247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>2.01</v>
+      </c>
       <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.03289406385219766</v>
+      </c>
       <c r="J23" s="2" t="n">
-        <v>1785</v>
+        <v>306953</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>754</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>non_nutritive_sweetener_intake</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>2.29</v>
-      </c>
+        <v>1.06</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>0.1888478627071757</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>188393</v>
+        <v>80388</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1814</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>whole_grain_intake</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>1.01</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>29.67</v>
+        <v>10.36</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>75.2</v>
+        <v>25.5</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.2815357195367387</v>
+        <v>0.7558207429534211</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>219042</v>
+        <v>8606</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5247</v>
+        <v>902</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>beta_carotene</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.91</v>
+        <v>1.61</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1.6</v>
+        <v>13.77</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>43</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.1482323029531308</v>
+        <v>0.007628590227997148</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>243154</v>
+        <v>339695</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1759</v>
+        <v>9964</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.01</v>
+        <v>2.93</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>80.8</v>
+        <v>74.7</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.03289406385219766</v>
+        <v>0.6690532512767781</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>306953</v>
+        <v>203999</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3788</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>13.77</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>0.007628590227997148</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="2" t="n">
-        <v>339695</v>
+        <v>2589</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>9964</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>72.8</v>
+        <v>43.3</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.2350417334910383</v>
+        <v>0.6752850576451785</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>161335</v>
+        <v>158299</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3086</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>avocado</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>2589</v>
+        <v>112328</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>avocado</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0.78</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
+        <v>0.99</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>1.69</v>
+      </c>
       <c r="H31" s="4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
+        <v>63.5</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.2952241724562409</v>
+      </c>
       <c r="J31" s="2" t="n">
-        <v>112328</v>
+        <v>309245</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1165</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>insoluble_dietary_fiber_intake</t>
+          <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>2374.62</v>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="inlineStr"/>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.06772651492216453</v>
+      </c>
       <c r="J32" s="2" t="n">
-        <v>101721</v>
+        <v>649414</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>776</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>plant_protein_intake</t>
+          <t>beta_carotene</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>0.83</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>58.7</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.829589986696913</v>
+        <v>0.8859913088116057</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>903751</v>
+        <v>368253</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2856</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>total_dietary_fiber_intake</t>
+          <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr"/>
@@ -1573,66 +1597,60 @@
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>676447</v>
+        <v>101721</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3990</v>
+        <v>776</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>plant_protein_intake</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0.71</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>1.58</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.2702316647251017</v>
-      </c>
+        <v>38.3</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>491062</v>
+        <v>585408</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5809</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>soluble_dietary_fiber_intake</t>
+          <t>total_dietary_fiber_intake</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
@@ -1641,233 +1659,233 @@
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>101721</v>
+        <v>676447</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>776</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>monounsaturated_fat_mufa</t>
+          <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2.16</v>
+        <v>1.08</v>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>91.8</v>
+        <v>0</v>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>547683</v>
+        <v>101721</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2981</v>
+        <v>776</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
+        <v>1.02</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>1.42</v>
+      </c>
       <c r="H38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
+        <v>83.7</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0.166366351579175</v>
+      </c>
       <c r="J38" s="2" t="n">
-        <v>101940</v>
+        <v>1003146</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>858</v>
+        <v>9243</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vitamin_b1</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>2.28</v>
-      </c>
+        <v>1.26</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.3069291525482077</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
-        <v>403230</v>
+        <v>37442</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1548</v>
+        <v>379</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.55</v>
+        <v>0.9</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1.31</v>
+      </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="n">
+        <v>0.03129320128944575</v>
+      </c>
       <c r="J40" s="2" t="n">
-        <v>574</v>
+        <v>222792</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>12</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>2.03</v>
-      </c>
+        <v>3.42</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0.02049876732164332</v>
-      </c>
+        <v>82.5</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="2" t="n">
-        <v>576384</v>
+        <v>1147</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>17242</v>
+        <v>522</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dietary_protein_intake</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>7.6</v>
+        <v>1.84</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.1010373025344448</v>
+        <v>0.02402104236253442</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>903751</v>
+        <v>580076</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2856</v>
+        <v>17811</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.99</v>
+        <v>0.55</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
@@ -1876,66 +1894,66 @@
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
-        <v>481419</v>
+        <v>574</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1001</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>vitamin_b1</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1.4</v>
+        <v>5.56</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>41.9</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.08520368090508293</v>
+        <v>0.6179106409432148</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>938913</v>
+        <v>575001</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14310</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>western_pattern_diet</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr"/>
@@ -1944,97 +1962,97 @@
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="2" t="n">
-        <v>388077</v>
+        <v>481419</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>822</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sugar_sweetened_beverage_intake</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5" t="inlineStr"/>
+        <v>41.9</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0.08520368090508293</v>
+      </c>
       <c r="J46" s="2" t="n">
-        <v>73024</v>
+        <v>938913</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>297</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>animal_protein_intake</t>
+          <t>western_pattern_diet</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1.03</v>
+        <v>0.86</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>2.18</v>
-      </c>
+        <v>1.37</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="5" t="n">
-        <v>0.4333336777261771</v>
-      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="2" t="n">
-        <v>903751</v>
+        <v>388077</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2856</v>
+        <v>822</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tomato</t>
+          <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr"/>
@@ -2043,66 +2061,60 @@
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="2" t="n">
-        <v>101683</v>
+        <v>73024</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>774</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dietary_protein_intake</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>2.24</v>
-      </c>
+        <v>1.23</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>0.01122317348460874</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="2" t="n">
-        <v>1417360</v>
+        <v>585408</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>6876</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>animal_protein_intake</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>3.01</v>
+        <v>1.27</v>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr"/>
@@ -2111,29 +2123,29 @@
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="2" t="n">
-        <v>586</v>
+        <v>585408</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>200</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>tomato</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>3.32</v>
+        <v>1.51</v>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr"/>
@@ -2142,91 +2154,97 @@
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="2" t="n">
-        <v>586</v>
+        <v>101683</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>200</v>
+        <v>774</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2.03</v>
+        <v>1.32</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
+        <v>1.57</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>2.24</v>
+      </c>
       <c r="H52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="inlineStr"/>
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.01122317348460874</v>
+      </c>
       <c r="J52" s="2" t="n">
-        <v>104440</v>
+        <v>1417360</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>206</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pickled_vegetables</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>3.1</v>
+        <v>1.51</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1.35</v>
+        <v>0.19</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>6.76</v>
+        <v>12.05</v>
       </c>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="4" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="2" t="n">
-        <v>260</v>
+        <v>32477</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>130</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vegetable_and_seed_oil_intake</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3.3</v>
+        <v>1.74</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>6.32</v>
+        <v>3.01</v>
       </c>
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr"/>
@@ -2235,29 +2253,29 @@
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="2" t="n">
-        <v>405</v>
+        <v>586</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>113</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>3.68</v>
+        <v>2.03</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2.59</v>
+        <v>1.15</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>5.24</v>
+        <v>3.56</v>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr"/>
@@ -2266,29 +2284,29 @@
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="2" t="n">
-        <v>1995</v>
+        <v>104440</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>355</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>pickled_vegetables</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>4.61</v>
+        <v>3.1</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>13.51</v>
+        <v>6.76</v>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr"/>
@@ -2297,29 +2315,29 @@
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="2" t="n">
-        <v>18244</v>
+        <v>260</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>61</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>anti_inflammatory_diet</t>
+          <t>vegetable_and_seed_oil_intake</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>5.21</v>
+        <v>3.3</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>15.47</v>
+        <v>6.32</v>
       </c>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr"/>
@@ -2328,14 +2346,76 @@
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>95</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:K59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
